--- a/instance/tournament_4_schedule.xlsx
+++ b/instance/tournament_4_schedule.xlsx
@@ -453,91 +453,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Schedule_Item_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Start_Time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>End_Time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Match_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Court</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Start_Time</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>End_Time</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Match_Type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Player1/Team1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Player2/Team2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Consecutive_Players</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Score1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Score2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Umpire</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -545,15 +550,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>239</v>
+        <v>527</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -570,57 +573,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0</v>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>211</v>
+        <v>528</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -637,57 +641,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>240</v>
+        <v>529</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -704,57 +709,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>244</v>
+        <v>530</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -771,57 +777,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Zhuoran Cheng / Yen Zhen Tan</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Chelsea Huang / Irwin Sunarto</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>250</v>
+        <v>531</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -838,57 +845,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Jiayi Shi / Haipeng Huang</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Shan Zhong / Fanghong Huang</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>217</v>
+        <v>532</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -905,57 +913,58 @@
           <t>19:20</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>210</v>
+        <v>533</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -972,61 +981,62 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>235</v>
+        <v>534</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1043,57 +1053,58 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>197</v>
+        <v>535</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1110,57 +1121,58 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Midy Tao</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Brandon Pham</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>190</v>
+        <v>536</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C11" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1177,57 +1189,58 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Haocheng Teng</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Zain Merchant</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>192</v>
+        <v>537</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -1244,61 +1257,62 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Jason Liu</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Ryuto Leegomonchai</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Jason Liu</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>0</v>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>204</v>
+        <v>538</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -1315,61 +1329,62 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Martin Lee</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Dominic Pang</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Dominic Pang</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>0</v>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>231</v>
+        <v>539</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -1386,57 +1401,58 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>209</v>
+        <v>540</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -1453,61 +1469,62 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh, Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>0</v>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>226</v>
+        <v>541</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1524,57 +1541,58 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>198</v>
+        <v>542</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1591,57 +1609,58 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>0</v>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>205</v>
+        <v>543</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C18" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1658,57 +1677,58 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
+          <t>Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Ines Bocanegra</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>193</v>
+        <v>544</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C19" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1725,57 +1745,58 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Avi Aswal</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Yuhung Kung</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>191</v>
+        <v>545</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1792,61 +1813,62 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>Haonan Wang</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0</v>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>212</v>
+        <v>546</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1863,61 +1885,62 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>Juncheng Tang, Yuhung Kung, Yifei Zheng</t>
-        </is>
-      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>0</v>
+          <t>Yuhung Kung, Juncheng Tang, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>237</v>
+        <v>547</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1934,61 +1957,62 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Yang Jiao</t>
-        </is>
-      </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung, Meghan Wong, Prathamesh Koranne</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
+          <t>Prathamesh Koranne, Meghan Wong</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>220</v>
+        <v>548</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -2005,57 +2029,58 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>0</v>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>207</v>
+        <v>549</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -2072,61 +2097,62 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh, Yuhung Kung, Prathamesh Koranne</t>
-        </is>
-      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
+          <t>Yuhung Kung, Manmeeth Nagesh, Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>214</v>
+        <v>550</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -2143,61 +2169,62 @@
           <t>20:20</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Juncheng Tang, Avi Aswal, Yifei Zheng</t>
-        </is>
-      </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0</v>
+          <t>Juncheng Tang, Yifei Zheng, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>232</v>
+        <v>551</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -2214,61 +2241,62 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>Meghan Wong</t>
-        </is>
-      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
+          <t>Elisa Liu, Meghan Wong</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>208</v>
+        <v>552</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -2285,61 +2313,62 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh, Avi Aswal, Haonan Wang, Prathamesh Koranne</t>
-        </is>
-      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0</v>
+          <t>Manmeeth Nagesh, Prathamesh Koranne, Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>241</v>
+        <v>553</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -2356,61 +2385,62 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Yang Jiao, Yifei Zheng, Bernice Tse Ling Tung</t>
-        </is>
-      </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>0</v>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>213</v>
+        <v>554</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -2427,61 +2457,62 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu, Yuhung Kung</t>
-        </is>
-      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
+          <t>Yuhung Kung, Jason Liu</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>238</v>
+        <v>555</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -2498,26 +2529,24 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
           <t>Junjie Zhou / Elisa Liu</t>
@@ -2525,34 +2554,37 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Prathamesh Koranne</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>0</v>
+          <t>Junjie Zhou, Elisa Liu, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>216</v>
+        <v>556</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -2569,61 +2601,62 @@
           <t>20:40</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>0</v>
+          <t>Prathamesh Koranne, Meghan Wong</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>242</v>
+        <v>557</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -2640,61 +2673,62 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Junjie Zhou / Elisa Liu</t>
-        </is>
-      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Yifei Zheng</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Elisa Liu, Reyna Wan, Yifei Zheng, Junjie Zhou</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0</v>
+          <t>Aryan Khandekar, Heng Wu, Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>215</v>
+        <v>558</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C33" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -2711,61 +2745,62 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
           <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar, Avi Aswal, Haonan Wang, Heng Wu</t>
-        </is>
-      </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
+          <t>Heng Wu, Aryan Khandekar, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>233</v>
+        <v>559</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -2782,61 +2817,62 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>Elisa Liu, Reyna Wan, Bernice Tse Ling Tung</t>
-        </is>
-      </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0</v>
+          <t>Reyna Wan, Elisa Liu, Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>201</v>
+        <v>560</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C35" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -2853,57 +2889,58 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>0</v>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>195</v>
+        <v>561</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C36" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
@@ -2920,57 +2957,58 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 3</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 4</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>0</v>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>194</v>
+        <v>562</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C37" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
@@ -2987,57 +3025,58 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>0</v>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>206</v>
+        <v>563</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -3054,57 +3093,58 @@
           <t>21:20</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>0</v>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>196</v>
+        <v>564</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -3121,84 +3161,79 @@
           <t>21:20</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>0</v>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
       </c>
       <c r="O39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" t="n">
         <v>7</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
+      <c r="C40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
         <v>7</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
         <v>7</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
+      <c r="C42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
         <v>7</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
+      <c r="C43" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="44"/>
@@ -3224,6 +3259,7 @@
       <c r="O45" s="4" t="inlineStr"/>
       <c r="P45" s="4" t="inlineStr"/>
       <c r="Q45" s="4" t="inlineStr"/>
+      <c r="R45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
@@ -3246,209 +3282,198 @@
       <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="n">
-        <v>17</v>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="47">
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>Consecutive 6 times</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Yifei Zheng</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>Consecutive 5 times</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Manmeeth Nagesh</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Meghan Wong</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Elisa Liu</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Juncheng Tang</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="J52" t="inlineStr">
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Meghan Wong</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Elisa Liu</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Reyna Wan</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Yang Jiao</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Junjie Zhou</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>
